--- a/requirements_acceptance_test_template.xlsx
+++ b/requirements_acceptance_test_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shoaf\Desktop\desktop\בראודה\סמסטרים\26-2\שיטות הנדסיות\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DA95014-1593-40C4-B8B0-9E89B51E918F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320C27EA-FA5B-4C1D-8A0F-4EF1F0A26F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{66F18C86-3E6B-4F2E-A3A6-956843228F2B}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="90">
   <si>
     <t>Req. number</t>
   </si>
@@ -77,9 +77,6 @@
     <t>system login is allowed only to workers and user's who have registered orders</t>
   </si>
   <si>
-    <t>system allows registration</t>
-  </si>
-  <si>
     <t>system allows permission management</t>
   </si>
   <si>
@@ -207,6 +204,105 @@
   </si>
   <si>
     <t>user can cancel order</t>
+  </si>
+  <si>
+    <t>system allows user registration</t>
+  </si>
+  <si>
+    <t>system allows identification</t>
+  </si>
+  <si>
+    <t>identification is done by using the ID that appears in the corresponding order</t>
+  </si>
+  <si>
+    <t>system allows order checking</t>
+  </si>
+  <si>
+    <t>checking order is done by using the entered order ID</t>
+  </si>
+  <si>
+    <t>checking order allows park entry if the corresponding order is active</t>
+  </si>
+  <si>
+    <t>system holds a counter: the current visitor count</t>
+  </si>
+  <si>
+    <t>after identification, system updates the counter according to the number of visitors written in the order</t>
+  </si>
+  <si>
+    <t>system allows fast identification</t>
+  </si>
+  <si>
+    <t>fast identification is done using a QR code</t>
+  </si>
+  <si>
+    <t>QR code is sent to the orderer upon order confirmation</t>
+  </si>
+  <si>
+    <t>system allows available space checking</t>
+  </si>
+  <si>
+    <t>system allows calculating available space</t>
+  </si>
+  <si>
+    <t>system allows exit registration</t>
+  </si>
+  <si>
+    <t>current visitor count update will change according to visitor count in the corresponding order</t>
+  </si>
+  <si>
+    <t>current visitor count update will change according to number entered by park worker</t>
+  </si>
+  <si>
+    <t>spontaneous visits will be allowed if system space availability check permits it</t>
+  </si>
+  <si>
+    <t>system updates the current visitor count upon exit registration (QR, ID, park worker)</t>
+  </si>
+  <si>
+    <t>available space count will be visible to: park manager, department manager</t>
+  </si>
+  <si>
+    <t>available space checking will be done by: park worker</t>
+  </si>
+  <si>
+    <t>sections</t>
+  </si>
+  <si>
+    <t>system allows park entry</t>
+  </si>
+  <si>
+    <t>payment bill will be calculated according to the pricing model</t>
+  </si>
+  <si>
+    <t>bill will be presented by the park worker to the visitors</t>
+  </si>
+  <si>
+    <t>system does not allow payment</t>
+  </si>
+  <si>
+    <t>system allows providing services</t>
+  </si>
+  <si>
+    <t>system provides entry payment bill</t>
+  </si>
+  <si>
+    <t>system allows calculating entry payment bill</t>
+  </si>
+  <si>
+    <t>calculating entry payment bill will be done individually per visitor</t>
+  </si>
+  <si>
+    <t>provided services are offered to visitors</t>
+  </si>
+  <si>
+    <t>entry payment bill will be calculated according to pricing model</t>
+  </si>
+  <si>
+    <t>the full price for one visitor will be set by the ministry of tourism</t>
+  </si>
+  <si>
+    <t>sale prices are unique parameters (refer to lines 21, 23)</t>
   </si>
 </sst>
 </file>
@@ -265,7 +361,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -287,6 +383,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF66FFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -318,7 +420,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -348,6 +450,11 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -667,7 +774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABE2F884-F2EF-4287-AC3D-5537D5275C3C}">
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -675,7 +782,7 @@
     <col min="3" max="3" width="25.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -685,8 +792,12 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="E1" s="13"/>
+      <c r="F1" s="15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="11">
         <v>1</v>
       </c>
@@ -697,7 +808,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
         <v>2</v>
       </c>
@@ -708,7 +819,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -719,7 +830,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -730,122 +841,122 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>5</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>6</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
       <c r="C10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>11</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>13</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
         <v>9</v>
@@ -856,7 +967,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
         <v>9</v>
@@ -867,7 +978,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
         <v>9</v>
@@ -878,7 +989,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
         <v>9</v>
@@ -889,7 +1000,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>3</v>
@@ -900,7 +1011,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>3</v>
@@ -911,7 +1022,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>3</v>
@@ -922,7 +1033,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C23" t="s">
         <v>9</v>
@@ -933,7 +1044,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s">
         <v>9</v>
@@ -944,7 +1055,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C25" t="s">
         <v>9</v>
@@ -955,7 +1066,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26" t="s">
         <v>9</v>
@@ -966,7 +1077,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>3</v>
@@ -977,7 +1088,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C28" t="s">
         <v>9</v>
@@ -988,7 +1099,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>3</v>
@@ -999,7 +1110,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C30" t="s">
         <v>9</v>
@@ -1010,7 +1121,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>3</v>
@@ -1021,7 +1132,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>3</v>
@@ -1032,7 +1143,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>3</v>
@@ -1043,7 +1154,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C34" t="s">
         <v>9</v>
@@ -1054,7 +1165,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C35" t="s">
         <v>9</v>
@@ -1065,7 +1176,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>3</v>
@@ -1076,7 +1187,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>3</v>
@@ -1087,7 +1198,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>3</v>
@@ -1098,7 +1209,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C39" t="s">
         <v>9</v>
@@ -1109,7 +1220,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C40" t="s">
         <v>9</v>
@@ -1120,7 +1231,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C41" t="s">
         <v>9</v>
@@ -1131,7 +1242,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C42" t="s">
         <v>9</v>
@@ -1142,7 +1253,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C43" s="12" t="s">
         <v>3</v>
@@ -1153,7 +1264,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C44" t="s">
         <v>9</v>
@@ -1164,7 +1275,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C45" t="s">
         <v>9</v>
@@ -1175,7 +1286,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" s="12" t="s">
         <v>3</v>
@@ -1186,7 +1297,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C47" t="s">
         <v>9</v>
@@ -1197,47 +1308,530 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="13">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
         <v>56</v>
       </c>
-      <c r="C48" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="s">
-        <v>57</v>
-      </c>
       <c r="C49" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A50">
+      <c r="D49" s="13"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" s="12">
         <v>49</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B50" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A52">
+      <c r="B51" t="s">
+        <v>59</v>
+      </c>
+      <c r="C51" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" s="12">
         <v>51</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A53">
+      <c r="B52" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="12">
         <v>52</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B53" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
+      <c r="B54" t="s">
+        <v>61</v>
+      </c>
+      <c r="C54" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>63</v>
+      </c>
+      <c r="C56" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>64</v>
+      </c>
+      <c r="C57" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" s="12">
+        <v>57</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>66</v>
+      </c>
+      <c r="C59" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>67</v>
+      </c>
+      <c r="C60" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" s="12">
+        <v>60</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" s="12">
+        <v>61</v>
+      </c>
+      <c r="B62" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C63" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" s="12">
+        <v>63</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C65" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C66" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C67" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C68" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" s="13">
+        <v>68</v>
+      </c>
+      <c r="B69" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C69" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" s="13"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" s="12">
+        <v>69</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C71" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C72" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73" s="12">
+        <v>72</v>
+      </c>
+      <c r="B73" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D73" s="13"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A74" s="12">
+        <v>73</v>
+      </c>
+      <c r="B74" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C75" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76" s="12">
+        <v>75</v>
+      </c>
+      <c r="B76" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77" s="14">
+        <v>76</v>
+      </c>
+      <c r="B77" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C77" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78" s="14">
+        <v>77</v>
+      </c>
+      <c r="B78" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C78" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A79" s="14">
+        <v>78</v>
+      </c>
+      <c r="B79" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C79" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A80" s="13">
+        <v>79</v>
+      </c>
+      <c r="B80" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C80" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81" s="14">
+        <v>80</v>
+      </c>
+      <c r="B81" s="14"/>
+      <c r="C81" s="14"/>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82" s="14">
+        <v>81</v>
+      </c>
+      <c r="B82" s="14"/>
+      <c r="C82" s="14"/>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A83" s="14">
+        <v>82</v>
+      </c>
+      <c r="B83" s="14"/>
+      <c r="C83" s="14"/>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84" s="14">
+        <v>83</v>
+      </c>
+      <c r="B84" s="14"/>
+      <c r="C84" s="14"/>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85" s="14">
+        <v>84</v>
+      </c>
+      <c r="B85" s="14"/>
+      <c r="C85" s="14"/>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86" s="14">
+        <v>85</v>
+      </c>
+      <c r="B86" s="14"/>
+      <c r="C86" s="14"/>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A87" s="14">
+        <v>86</v>
+      </c>
+      <c r="B87" s="14"/>
+      <c r="C87" s="14"/>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A88" s="14">
+        <v>87</v>
+      </c>
+      <c r="B88" s="14"/>
+      <c r="C88" s="14"/>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A89" s="14">
+        <v>88</v>
+      </c>
+      <c r="B89" s="14"/>
+      <c r="C89" s="14"/>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A90" s="14">
+        <v>89</v>
+      </c>
+      <c r="B90" s="14"/>
+      <c r="C90" s="14"/>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A91" s="14">
+        <v>90</v>
+      </c>
+      <c r="B91" s="14"/>
+      <c r="C91" s="14"/>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A92" s="14">
+        <v>91</v>
+      </c>
+      <c r="B92" s="14"/>
+      <c r="C92" s="14"/>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A93" s="14">
+        <v>92</v>
+      </c>
+      <c r="B93" s="14"/>
+      <c r="C93" s="14"/>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A94" s="14">
+        <v>93</v>
+      </c>
+      <c r="B94" s="14"/>
+      <c r="C94" s="14"/>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A95" s="14">
+        <v>94</v>
+      </c>
+      <c r="B95" s="14"/>
+      <c r="C95" s="14"/>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A96" s="14">
+        <v>95</v>
+      </c>
+      <c r="B96" s="14"/>
+      <c r="C96" s="14"/>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A97" s="14">
+        <v>96</v>
+      </c>
+      <c r="B97" s="14"/>
+      <c r="C97" s="14"/>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A98" s="14">
+        <v>97</v>
+      </c>
+      <c r="B98" s="14"/>
+      <c r="C98" s="14"/>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A99" s="14">
+        <v>98</v>
+      </c>
+      <c r="B99" s="14"/>
+      <c r="C99" s="14"/>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A100" s="14">
+        <v>99</v>
+      </c>
+      <c r="B100" s="14"/>
+      <c r="C100" s="14"/>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A101" s="14">
+        <v>100</v>
+      </c>
+      <c r="B101" s="14"/>
+      <c r="C101" s="14"/>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A102" s="14">
+        <v>101</v>
+      </c>
+      <c r="B102" s="14"/>
+      <c r="C102" s="14"/>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A103" s="14"/>
+      <c r="B103" s="14"/>
+      <c r="C103" s="14"/>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A104" s="14"/>
+      <c r="B104" s="14"/>
+      <c r="C104" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
